--- a/Data_example.xlsx
+++ b/Data_example.xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ksuemailprod-my.sharepoint.com/personal/groa_ksu_edu/Documents/Projects/Bayesian - P Fertilizer/BM_P_data_analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ksuemailprod-my.sharepoint.com/personal/groa_ksu_edu/Documents/Projects/Bayesian - P Fertilizer/Bayesian_CSTV_review/Code &amp; data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="120" documentId="11_EC7CFDCE8F79A8D366075C52F34BF277ED7DF3C9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53C8EA39-5EF1-4C50-BED0-30FA2F611B8D}"/>
+  <xr:revisionPtr revIDLastSave="121" documentId="11_EC7CFDCE8F79A8D366075C52F34BF277ED7DF3C9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D9EA833-4B17-4B32-97BE-11D87C88F01C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KS_30" sheetId="7" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -33,15 +36,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>input_level</t>
   </si>
   <si>
     <t>response</t>
-  </si>
-  <si>
-    <t>site</t>
   </si>
 </sst>
 </file>
@@ -402,390 +402,293 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E021CE34-DE6B-4CF3-9C33-AF7F65E76BB9}">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="2" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
+      <c r="C1" s="1"/>
+    </row>
+    <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>20.25</v>
       </c>
       <c r="B2" s="2">
-        <v>20.25</v>
-      </c>
-      <c r="C2" s="2">
         <v>88.502411009539657</v>
       </c>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
+      <c r="C2" s="2"/>
+    </row>
+    <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>45.75</v>
       </c>
       <c r="B3" s="2">
-        <v>45.75</v>
-      </c>
-      <c r="C3" s="2">
         <v>90.861831822852977</v>
       </c>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>11.333333333333334</v>
       </c>
       <c r="B4" s="2">
-        <v>11.333333333333334</v>
-      </c>
-      <c r="C4" s="2">
         <v>91.680703902650251</v>
       </c>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
+      <c r="C4" s="2"/>
+    </row>
+    <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>6.75</v>
       </c>
       <c r="B5" s="2">
-        <v>6.75</v>
-      </c>
-      <c r="C5" s="2">
         <v>83.658282476376684</v>
       </c>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>4.75</v>
       </c>
       <c r="B6" s="2">
-        <v>4.75</v>
-      </c>
-      <c r="C6" s="2">
         <v>68.320569809575375</v>
       </c>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>46.5</v>
       </c>
       <c r="B7" s="2">
-        <v>46.5</v>
-      </c>
-      <c r="C7" s="2">
         <v>94.143475533089273</v>
       </c>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>7</v>
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>25.333333333333332</v>
       </c>
       <c r="B8" s="2">
-        <v>25.333333333333332</v>
-      </c>
-      <c r="C8" s="2">
         <v>95.685516541884112</v>
       </c>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>8</v>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>21</v>
       </c>
       <c r="B9" s="2">
-        <v>21</v>
-      </c>
-      <c r="C9" s="2">
         <v>86.151136209223637</v>
       </c>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>43</v>
       </c>
       <c r="B10" s="2">
-        <v>43</v>
-      </c>
-      <c r="C10" s="2">
         <v>91.851403022690818</v>
       </c>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>10</v>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>25.666666666666668</v>
       </c>
       <c r="B11" s="2">
-        <v>25.666666666666668</v>
-      </c>
-      <c r="C11" s="2">
         <v>88.625313060187338</v>
       </c>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>11</v>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>22.25</v>
       </c>
       <c r="B12" s="2">
-        <v>22.25</v>
-      </c>
-      <c r="C12" s="2">
         <v>88.062182386748134</v>
       </c>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>12</v>
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>39.75</v>
       </c>
       <c r="B13" s="2">
-        <v>39.75</v>
-      </c>
-      <c r="C13" s="2">
         <v>95.326194749241679</v>
       </c>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>13</v>
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>12.5</v>
       </c>
       <c r="B14" s="2">
-        <v>12.5</v>
-      </c>
-      <c r="C14" s="2">
         <v>88.240024898467766</v>
       </c>
-      <c r="D14" s="2"/>
-    </row>
-    <row r="15" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>14</v>
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>13.25</v>
       </c>
       <c r="B15" s="2">
+        <v>93.41834974091941</v>
+      </c>
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>18</v>
+      </c>
+      <c r="B16" s="2">
+        <v>81.13017261699828</v>
+      </c>
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>2.25</v>
+      </c>
+      <c r="B17" s="2">
+        <v>73.071408546716995</v>
+      </c>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>4.25</v>
+      </c>
+      <c r="B18" s="2">
+        <v>91.303427931000144</v>
+      </c>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>5.25</v>
+      </c>
+      <c r="B19" s="2">
+        <v>79.65886561247568</v>
+      </c>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="B20" s="2">
+        <v>82.319978267607041</v>
+      </c>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>23.75</v>
+      </c>
+      <c r="B21" s="2">
+        <v>90</v>
+      </c>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>20.666666666666668</v>
+      </c>
+      <c r="B22" s="2">
+        <v>86.413130768312399</v>
+      </c>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>2.75</v>
+      </c>
+      <c r="B23" s="2">
+        <v>74.865362422568538</v>
+      </c>
+      <c r="C23" s="2"/>
+    </row>
+    <row r="24" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>4.25</v>
+      </c>
+      <c r="B24" s="2">
+        <v>77.545963526864995</v>
+      </c>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
         <v>13.25</v>
       </c>
-      <c r="C15" s="2">
-        <v>93.41834974091941</v>
-      </c>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2">
-        <v>18</v>
-      </c>
-      <c r="C16" s="2">
-        <v>81.13017261699828</v>
-      </c>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2">
-        <v>2.25</v>
-      </c>
-      <c r="C17" s="2">
-        <v>73.071408546716995</v>
-      </c>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2">
-        <v>4.25</v>
-      </c>
-      <c r="C18" s="2">
-        <v>91.303427931000144</v>
-      </c>
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2">
-        <v>5.25</v>
-      </c>
-      <c r="C19" s="2">
-        <v>79.65886561247568</v>
-      </c>
-      <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2">
-        <v>5.5</v>
-      </c>
-      <c r="C20" s="2">
-        <v>82.319978267607041</v>
-      </c>
-      <c r="D20" s="2"/>
-    </row>
-    <row r="21" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2">
-        <v>23.75</v>
-      </c>
-      <c r="C21" s="2">
-        <v>90</v>
-      </c>
-      <c r="D21" s="2"/>
-    </row>
-    <row r="22" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2">
-        <v>20.666666666666668</v>
-      </c>
-      <c r="C22" s="2">
-        <v>86.413130768312399</v>
-      </c>
-      <c r="D22" s="2"/>
-    </row>
-    <row r="23" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2">
-        <v>2.75</v>
-      </c>
-      <c r="C23" s="2">
-        <v>74.865362422568538</v>
-      </c>
-      <c r="D23" s="2"/>
-    </row>
-    <row r="24" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2">
-        <v>4.25</v>
-      </c>
-      <c r="C24" s="2">
-        <v>77.545963526864995</v>
-      </c>
-      <c r="D24" s="2"/>
-    </row>
-    <row r="25" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25">
+      <c r="B25" s="2">
+        <v>94.106866469205315</v>
+      </c>
+      <c r="C25" s="2"/>
+    </row>
+    <row r="26" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
         <v>24</v>
       </c>
-      <c r="B25" s="2">
-        <v>13.25</v>
-      </c>
-      <c r="C25" s="2">
-        <v>94.106866469205315</v>
-      </c>
-      <c r="D25" s="2"/>
-    </row>
-    <row r="26" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>25</v>
-      </c>
       <c r="B26" s="2">
-        <v>24</v>
-      </c>
-      <c r="C26" s="2">
         <v>85</v>
       </c>
-      <c r="D26" s="2"/>
-    </row>
-    <row r="27" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>26</v>
+      <c r="C26" s="2"/>
+    </row>
+    <row r="27" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>33.5</v>
       </c>
       <c r="B27" s="2">
-        <v>33.5</v>
-      </c>
-      <c r="C27" s="2">
         <v>90.701198317041218</v>
       </c>
-      <c r="D27" s="2"/>
-    </row>
-    <row r="28" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>27</v>
+      <c r="C27" s="2"/>
+    </row>
+    <row r="28" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>7.666666666666667</v>
       </c>
       <c r="B28" s="2">
-        <v>7.666666666666667</v>
-      </c>
-      <c r="C28" s="2">
         <v>72.341599387102235</v>
       </c>
-      <c r="D28" s="2"/>
-    </row>
-    <row r="29" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>28</v>
+      <c r="C28" s="2"/>
+    </row>
+    <row r="29" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>14.5</v>
       </c>
       <c r="B29" s="2">
+        <v>91.702423076501233</v>
+      </c>
+      <c r="C29" s="2"/>
+    </row>
+    <row r="30" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
         <v>14.5</v>
       </c>
-      <c r="C29" s="2">
-        <v>91.702423076501233</v>
-      </c>
-      <c r="D29" s="2"/>
-    </row>
-    <row r="30" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>29</v>
-      </c>
       <c r="B30" s="2">
-        <v>14.5</v>
-      </c>
-      <c r="C30" s="2">
         <v>89.082518144707521</v>
       </c>
-      <c r="D30" s="2"/>
-    </row>
-    <row r="31" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>30</v>
+      <c r="C30" s="2"/>
+    </row>
+    <row r="31" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>4.5</v>
       </c>
       <c r="B31" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="C31" s="2">
         <v>93.163935211714488</v>
       </c>
-      <c r="D31" s="2"/>
+      <c r="C31" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C31">
-    <sortCondition ref="A2:A31"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>